--- a/src/main/resources/templates/协议类型导入模板.xlsx
+++ b/src/main/resources/templates/协议类型导入模板.xlsx
@@ -27,15 +27,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>类型编码</t>
+    <t>协议编码</t>
   </si>
   <si>
-    <t>名称</t>
+    <t>协议名称</t>
   </si>
   <si>
-    <t>适用系统类型</t>
+    <t>协议分类</t>
+  </si>
+  <si>
+    <t>系统类型</t>
   </si>
   <si>
     <t>状态</t>
@@ -63,15 +66,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -543,7 +547,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,10 +699,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1234,21 +1238,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="22.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="17.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="38.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="14.5" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1257,8 +1262,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
